--- a/public/template_barang.xlsx
+++ b/public/template_barang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hype AMD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5A9200-C08D-4B9B-8F95-811013478743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B9F50-FFD8-400D-9905-ABC4F9C2C5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4596" yWindow="7080" windowWidth="17280" windowHeight="9420" xr2:uid="{BB31953B-2057-474D-965F-778755BE071E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>kategori_id</t>
   </si>
@@ -57,25 +57,22 @@
     <t>harga_jual</t>
   </si>
   <si>
-    <t>stok</t>
-  </si>
-  <si>
-    <t>sereal cokelat 150g</t>
-  </si>
-  <si>
-    <t>kopi bubuk</t>
-  </si>
-  <si>
-    <t>pengharum ruangan otomatis</t>
-  </si>
-  <si>
-    <t>B100</t>
-  </si>
-  <si>
-    <t>B101</t>
-  </si>
-  <si>
-    <t>B102</t>
+    <t>B017</t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>sereal stroberi 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kopi instan </t>
+  </si>
+  <si>
+    <t>pengharum dapur otomatis</t>
   </si>
 </sst>
 </file>
@@ -146,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -156,12 +153,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192606ED-D36E-405D-823B-CB59FA73EAFB}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -493,17 +484,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>6</v>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>6</v>
       </c>
@@ -511,22 +499,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>10000</v>
       </c>
       <c r="F2" s="2">
-        <v>10000</v>
-      </c>
-      <c r="G2" s="2">
         <v>15000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -534,22 +519,19 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5000</v>
       </c>
       <c r="F3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="G3" s="2">
         <v>7000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="69" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -557,18 +539,15 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20000</v>
       </c>
       <c r="F4" s="2">
-        <v>20000</v>
-      </c>
-      <c r="G4" s="2">
         <v>25000</v>
       </c>
     </row>
